--- a/outputs/test53_report.xlsx
+++ b/outputs/test53_report.xlsx
@@ -3,12 +3,21 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Events" sheetId="2" r:id="rId2"/>
-    <sheet name="Parameters" sheetId="3" r:id="rId3"/>
-    <sheet name="OperationalDefinitions" sheetId="4" r:id="rId4"/>
-    <sheet name="Provenance" sheetId="5" r:id="rId5"/>
+    <sheet name="Results" sheetId="1" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" r:id="rId2"/>
+    <sheet name="Events" sheetId="3" r:id="rId3"/>
+    <sheet name="Parameters" sheetId="4" r:id="rId4"/>
+    <sheet name="OperationalDefinitions" sheetId="5" r:id="rId5"/>
+    <sheet name="Provenance" sheetId="6" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Results'!A1:Z2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Summary'!A1:EV2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'Events'!A1:X7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3">'Parameters'!A1:C42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'OperationalDefinitions'!A1:F17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5">'Provenance'!A1:U2</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -401,7 +410,361 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z2"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="28.83203125" customWidth="1"/>
+    <col min="8" max="8" width="44.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="16.83203125" customWidth="1"/>
+    <col min="13" max="13" width="16.83203125" customWidth="1"/>
+    <col min="14" max="14" width="14.83203125" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" customWidth="1"/>
+    <col min="16" max="16" width="14.83203125" customWidth="1"/>
+    <col min="17" max="17" width="14.83203125" customWidth="1"/>
+    <col min="18" max="18" width="14.83203125" customWidth="1"/>
+    <col min="19" max="19" width="12.83203125" customWidth="1"/>
+    <col min="20" max="20" width="12.83203125" customWidth="1"/>
+    <col min="21" max="21" width="18.83203125" customWidth="1"/>
+    <col min="22" max="22" width="18.83203125" customWidth="1"/>
+    <col min="23" max="23" width="18.83203125" customWidth="1"/>
+    <col min="24" max="24" width="18.83203125" customWidth="1"/>
+    <col min="25" max="25" width="14.83203125" customWidth="1"/>
+    <col min="26" max="26" width="16.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>fileName</v>
+      </c>
+      <c r="B1" t="str">
+        <v>label</v>
+      </c>
+      <c r="C1" t="str">
+        <v>measurementBasis</v>
+      </c>
+      <c r="D1" t="str">
+        <v>targetStatus</v>
+      </c>
+      <c r="E1" t="str">
+        <v>targetHole</v>
+      </c>
+      <c r="F1" t="str">
+        <v>scaleStatus</v>
+      </c>
+      <c r="G1" t="str">
+        <v>physicalScale</v>
+      </c>
+      <c r="H1" t="str">
+        <v>escapeState</v>
+      </c>
+      <c r="I1" t="str">
+        <v>eventsReviewStatus</v>
+      </c>
+      <c r="J1" t="str">
+        <v>primaryLatency</v>
+      </c>
+      <c r="K1" t="str">
+        <v>totalLatency</v>
+      </c>
+      <c r="L1" t="str">
+        <v>primaryErrors</v>
+      </c>
+      <c r="M1" t="str">
+        <v>totalErrors</v>
+      </c>
+      <c r="N1" t="str">
+        <v>primaryErrorsConfirmedCount</v>
+      </c>
+      <c r="O1" t="str">
+        <v>primaryErrorsProvisionalCount</v>
+      </c>
+      <c r="P1" t="str">
+        <v>totalErrorsConfirmedCount</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>totalErrorsProvisionalCount</v>
+      </c>
+      <c r="R1" t="str">
+        <v>pathLength</v>
+      </c>
+      <c r="S1" t="str">
+        <v>meanSpeed</v>
+      </c>
+      <c r="T1" t="str">
+        <v>maxSpeed</v>
+      </c>
+      <c r="U1" t="str">
+        <v>meanSpeedDiagnostic</v>
+      </c>
+      <c r="V1" t="str">
+        <v>maxSpeedDiagnostic</v>
+      </c>
+      <c r="W1" t="str">
+        <v>targetQuadrantFraction</v>
+      </c>
+      <c r="X1" t="str">
+        <v>targetQuadrantTime</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>searchStrategy</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>searchStrategyOverride</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>test53.mp4</v>
+      </c>
+      <c r="B2" t="str">
+        <v>test53</v>
+      </c>
+      <c r="C2" t="str">
+        <v>corrected</v>
+      </c>
+      <c r="D2" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="F2" t="str">
+        <v>unknown</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Unknown (coordinates in px)</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Completion at 24.400000 s; 24.40 s total latency — candidate hole completion; protocol target not confirmed</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Current</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Unavailable (Target hole not confirmed.)</v>
+      </c>
+      <c r="K2" t="str">
+        <v>24.40 s</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Unavailable (Target hole not confirmed.)</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Unavailable (Target hole not confirmed.)</v>
+      </c>
+      <c r="N2" t="str">
+        <v>Target hole not confirmed.</v>
+      </c>
+      <c r="O2" t="str">
+        <v>Target hole not confirmed.</v>
+      </c>
+      <c r="P2" t="str">
+        <v>Target hole not confirmed.</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>Target hole not confirmed.</v>
+      </c>
+      <c r="R2" t="str">
+        <v>527.39 px</v>
+      </c>
+      <c r="S2" t="str">
+        <v>19.89 px/s</v>
+      </c>
+      <c r="T2" t="str">
+        <v>115.13 px/s</v>
+      </c>
+      <c r="U2" t="str">
+        <v>20.25 px/s</v>
+      </c>
+      <c r="V2" t="str">
+        <v>44162.60 px/s</v>
+      </c>
+      <c r="W2" t="str">
+        <v>Unavailable (Target hole not confirmed.)</v>
+      </c>
+      <c r="X2" t="str">
+        <v>Unavailable (Target hole not confirmed.)</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>unclassified</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>—</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Z2"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:EV2"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+    <col min="14" max="14" width="14.83203125" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" customWidth="1"/>
+    <col min="16" max="16" width="14.83203125" customWidth="1"/>
+    <col min="17" max="17" width="14.83203125" customWidth="1"/>
+    <col min="18" max="18" width="14.83203125" customWidth="1"/>
+    <col min="19" max="19" width="14.83203125" customWidth="1"/>
+    <col min="20" max="20" width="14.83203125" customWidth="1"/>
+    <col min="21" max="21" width="14.83203125" customWidth="1"/>
+    <col min="22" max="22" width="14.83203125" customWidth="1"/>
+    <col min="23" max="23" width="14.83203125" customWidth="1"/>
+    <col min="24" max="24" width="14.83203125" customWidth="1"/>
+    <col min="25" max="25" width="14.83203125" customWidth="1"/>
+    <col min="26" max="26" width="14.83203125" customWidth="1"/>
+    <col min="27" max="27" width="14.83203125" customWidth="1"/>
+    <col min="28" max="28" width="14.83203125" customWidth="1"/>
+    <col min="29" max="29" width="14.83203125" customWidth="1"/>
+    <col min="30" max="30" width="14.83203125" customWidth="1"/>
+    <col min="31" max="31" width="14.83203125" customWidth="1"/>
+    <col min="32" max="32" width="14.83203125" customWidth="1"/>
+    <col min="33" max="33" width="14.83203125" customWidth="1"/>
+    <col min="34" max="34" width="14.83203125" customWidth="1"/>
+    <col min="35" max="35" width="14.83203125" customWidth="1"/>
+    <col min="36" max="36" width="14.83203125" customWidth="1"/>
+    <col min="37" max="37" width="14.83203125" customWidth="1"/>
+    <col min="38" max="38" width="14.83203125" customWidth="1"/>
+    <col min="39" max="39" width="14.83203125" customWidth="1"/>
+    <col min="40" max="40" width="14.83203125" customWidth="1"/>
+    <col min="41" max="41" width="14.83203125" customWidth="1"/>
+    <col min="42" max="42" width="14.83203125" customWidth="1"/>
+    <col min="43" max="43" width="14.83203125" customWidth="1"/>
+    <col min="44" max="44" width="14.83203125" customWidth="1"/>
+    <col min="45" max="45" width="14.83203125" customWidth="1"/>
+    <col min="46" max="46" width="14.83203125" customWidth="1"/>
+    <col min="47" max="47" width="14.83203125" customWidth="1"/>
+    <col min="48" max="48" width="14.83203125" customWidth="1"/>
+    <col min="49" max="49" width="14.83203125" customWidth="1"/>
+    <col min="50" max="50" width="14.83203125" customWidth="1"/>
+    <col min="51" max="51" width="14.83203125" customWidth="1"/>
+    <col min="52" max="52" width="14.83203125" customWidth="1"/>
+    <col min="53" max="53" width="14.83203125" customWidth="1"/>
+    <col min="54" max="54" width="14.83203125" customWidth="1"/>
+    <col min="55" max="55" width="14.83203125" customWidth="1"/>
+    <col min="56" max="56" width="14.83203125" customWidth="1"/>
+    <col min="57" max="57" width="14.83203125" customWidth="1"/>
+    <col min="58" max="58" width="14.83203125" customWidth="1"/>
+    <col min="59" max="59" width="14.83203125" customWidth="1"/>
+    <col min="60" max="60" width="14.83203125" customWidth="1"/>
+    <col min="61" max="61" width="14.83203125" customWidth="1"/>
+    <col min="62" max="62" width="14.83203125" customWidth="1"/>
+    <col min="63" max="63" width="14.83203125" customWidth="1"/>
+    <col min="64" max="64" width="14.83203125" customWidth="1"/>
+    <col min="65" max="65" width="14.83203125" customWidth="1"/>
+    <col min="66" max="66" width="14.83203125" customWidth="1"/>
+    <col min="67" max="67" width="14.83203125" customWidth="1"/>
+    <col min="68" max="68" width="14.83203125" customWidth="1"/>
+    <col min="69" max="69" width="14.83203125" customWidth="1"/>
+    <col min="70" max="70" width="14.83203125" customWidth="1"/>
+    <col min="71" max="71" width="14.83203125" customWidth="1"/>
+    <col min="72" max="72" width="14.83203125" customWidth="1"/>
+    <col min="73" max="73" width="14.83203125" customWidth="1"/>
+    <col min="74" max="74" width="14.83203125" customWidth="1"/>
+    <col min="75" max="75" width="14.83203125" customWidth="1"/>
+    <col min="76" max="76" width="14.83203125" customWidth="1"/>
+    <col min="77" max="77" width="14.83203125" customWidth="1"/>
+    <col min="78" max="78" width="14.83203125" customWidth="1"/>
+    <col min="79" max="79" width="14.83203125" customWidth="1"/>
+    <col min="80" max="80" width="14.83203125" customWidth="1"/>
+    <col min="81" max="81" width="14.83203125" customWidth="1"/>
+    <col min="82" max="82" width="14.83203125" customWidth="1"/>
+    <col min="83" max="83" width="14.83203125" customWidth="1"/>
+    <col min="84" max="84" width="14.83203125" customWidth="1"/>
+    <col min="85" max="85" width="14.83203125" customWidth="1"/>
+    <col min="86" max="86" width="14.83203125" customWidth="1"/>
+    <col min="87" max="87" width="14.83203125" customWidth="1"/>
+    <col min="88" max="88" width="14.83203125" customWidth="1"/>
+    <col min="89" max="89" width="14.83203125" customWidth="1"/>
+    <col min="90" max="90" width="14.83203125" customWidth="1"/>
+    <col min="91" max="91" width="14.83203125" customWidth="1"/>
+    <col min="92" max="92" width="14.83203125" customWidth="1"/>
+    <col min="93" max="93" width="14.83203125" customWidth="1"/>
+    <col min="94" max="94" width="14.83203125" customWidth="1"/>
+    <col min="95" max="95" width="14.83203125" customWidth="1"/>
+    <col min="96" max="96" width="14.83203125" customWidth="1"/>
+    <col min="97" max="97" width="14.83203125" customWidth="1"/>
+    <col min="98" max="98" width="14.83203125" customWidth="1"/>
+    <col min="99" max="99" width="14.83203125" customWidth="1"/>
+    <col min="100" max="100" width="14.83203125" customWidth="1"/>
+    <col min="101" max="101" width="14.83203125" customWidth="1"/>
+    <col min="102" max="102" width="14.83203125" customWidth="1"/>
+    <col min="103" max="103" width="14.83203125" customWidth="1"/>
+    <col min="104" max="104" width="14.83203125" customWidth="1"/>
+    <col min="105" max="105" width="14.83203125" customWidth="1"/>
+    <col min="106" max="106" width="14.83203125" customWidth="1"/>
+    <col min="107" max="107" width="14.83203125" customWidth="1"/>
+    <col min="108" max="108" width="14.83203125" customWidth="1"/>
+    <col min="109" max="109" width="14.83203125" customWidth="1"/>
+    <col min="110" max="110" width="14.83203125" customWidth="1"/>
+    <col min="111" max="111" width="14.83203125" customWidth="1"/>
+    <col min="112" max="112" width="14.83203125" customWidth="1"/>
+    <col min="113" max="113" width="14.83203125" customWidth="1"/>
+    <col min="114" max="114" width="14.83203125" customWidth="1"/>
+    <col min="115" max="115" width="14.83203125" customWidth="1"/>
+    <col min="116" max="116" width="14.83203125" customWidth="1"/>
+    <col min="117" max="117" width="14.83203125" customWidth="1"/>
+    <col min="118" max="118" width="14.83203125" customWidth="1"/>
+    <col min="119" max="119" width="14.83203125" customWidth="1"/>
+    <col min="120" max="120" width="14.83203125" customWidth="1"/>
+    <col min="121" max="121" width="14.83203125" customWidth="1"/>
+    <col min="122" max="122" width="14.83203125" customWidth="1"/>
+    <col min="123" max="123" width="14.83203125" customWidth="1"/>
+    <col min="124" max="124" width="14.83203125" customWidth="1"/>
+    <col min="125" max="125" width="14.83203125" customWidth="1"/>
+    <col min="126" max="126" width="14.83203125" customWidth="1"/>
+    <col min="127" max="127" width="14.83203125" customWidth="1"/>
+    <col min="128" max="128" width="14.83203125" customWidth="1"/>
+    <col min="129" max="129" width="14.83203125" customWidth="1"/>
+    <col min="130" max="130" width="14.83203125" customWidth="1"/>
+    <col min="131" max="131" width="14.83203125" customWidth="1"/>
+    <col min="132" max="132" width="14.83203125" customWidth="1"/>
+    <col min="133" max="133" width="14.83203125" customWidth="1"/>
+    <col min="134" max="134" width="14.83203125" customWidth="1"/>
+    <col min="135" max="135" width="14.83203125" customWidth="1"/>
+    <col min="136" max="136" width="14.83203125" customWidth="1"/>
+    <col min="137" max="137" width="14.83203125" customWidth="1"/>
+    <col min="138" max="138" width="14.83203125" customWidth="1"/>
+    <col min="139" max="139" width="14.83203125" customWidth="1"/>
+    <col min="140" max="140" width="14.83203125" customWidth="1"/>
+    <col min="141" max="141" width="14.83203125" customWidth="1"/>
+    <col min="142" max="142" width="14.83203125" customWidth="1"/>
+    <col min="143" max="143" width="14.83203125" customWidth="1"/>
+    <col min="144" max="144" width="14.83203125" customWidth="1"/>
+    <col min="145" max="145" width="14.83203125" customWidth="1"/>
+    <col min="146" max="146" width="14.83203125" customWidth="1"/>
+    <col min="147" max="147" width="14.83203125" customWidth="1"/>
+    <col min="148" max="148" width="14.83203125" customWidth="1"/>
+    <col min="149" max="149" width="14.83203125" customWidth="1"/>
+    <col min="150" max="150" width="14.83203125" customWidth="1"/>
+    <col min="151" max="151" width="14.83203125" customWidth="1"/>
+    <col min="152" max="152" width="14.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -896,7 +1259,7 @@
         <v>2026-09-07T18:12:26.576Z</v>
       </c>
       <c r="P2" t="str">
-        <v>2026-09-07T19:54:09.009Z</v>
+        <v>2026-09-07T20:08:18.624Z</v>
       </c>
       <c r="Q2" t="str">
         <v>false</v>
@@ -907,18 +1270,6 @@
       <c r="T2" t="str">
         <v>unclassified</v>
       </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
       <c r="AA2" t="str">
         <v>unavailable</v>
       </c>
@@ -1158,129 +1509,118 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:EV2"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:EV2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:X7"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="36.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="28.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="16.83203125" customWidth="1"/>
+    <col min="13" max="13" width="16.83203125" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" customWidth="1"/>
+    <col min="16" max="16" width="12.83203125" customWidth="1"/>
+    <col min="17" max="17" width="10.83203125" customWidth="1"/>
+    <col min="18" max="18" width="10.83203125" customWidth="1"/>
+    <col min="19" max="19" width="14.83203125" customWidth="1"/>
+    <col min="20" max="20" width="14.83203125" customWidth="1"/>
+    <col min="21" max="21" width="18.83203125" customWidth="1"/>
+    <col min="22" max="22" width="24.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>trialId</v>
-      </c>
-      <c r="B1" t="str">
-        <v>eventId</v>
-      </c>
-      <c r="C1" t="str">
-        <v>type</v>
-      </c>
-      <c r="D1" t="str">
-        <v>exportLabel</v>
-      </c>
-      <c r="E1" t="str">
-        <v>holeDisplay</v>
-      </c>
-      <c r="F1" t="str">
-        <v>holeIdInternal</v>
-      </c>
-      <c r="G1" t="str">
-        <v>startFrameIndex</v>
-      </c>
-      <c r="H1" t="str">
-        <v>endFrameIndex</v>
-      </c>
-      <c r="I1" t="str">
-        <v>startTimeSec</v>
-      </c>
-      <c r="J1" t="str">
-        <v>endTimeSec</v>
-      </c>
-      <c r="K1" t="str">
-        <v>entryOnsetTimeSec</v>
-      </c>
-      <c r="L1" t="str">
-        <v>completionTimeSec</v>
-      </c>
-      <c r="M1" t="str">
-        <v>censorBoundaryTimeSec</v>
-      </c>
-      <c r="N1" t="str">
-        <v>origin</v>
-      </c>
-      <c r="O1" t="str">
-        <v>status</v>
-      </c>
-      <c r="P1" t="str">
-        <v>confidence</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>visitIndex</v>
-      </c>
-      <c r="R1" t="str">
-        <v>isRevisit</v>
-      </c>
-      <c r="S1" t="str">
-        <v>bodyEntryPath</v>
-      </c>
-      <c r="T1" t="str">
-        <v>bodyEntryVersion</v>
-      </c>
-      <c r="U1" t="str">
-        <v>pixelEvidenceComplete</v>
-      </c>
-      <c r="V1" t="str">
-        <v>notes</v>
+        <v>Frame indices: startFrameIndex and endFrameIndex are 0-based internal decoder indices. startFrameDisplay and endFrameDisplay add 1 for human-readable frame numbers.</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>8df6325a-52d4-482b-a20f-688ba96ae0f5</v>
+        <v>trialId</v>
       </c>
       <c r="B2" t="str">
-        <v>b20de175-42d7-4c55-b8c8-32a957caf29c</v>
+        <v>eventId</v>
       </c>
       <c r="C2" t="str">
-        <v>investigation</v>
+        <v>type</v>
       </c>
       <c r="D2" t="str">
-        <v>investigation</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>150</v>
-      </c>
-      <c r="H2">
-        <v>265</v>
-      </c>
-      <c r="I2">
-        <v>5.066667</v>
-      </c>
-      <c r="J2">
-        <v>8.9</v>
+        <v>exportLabel</v>
+      </c>
+      <c r="E2" t="str">
+        <v>holeDisplay</v>
+      </c>
+      <c r="F2" t="str">
+        <v>holeIdInternal</v>
+      </c>
+      <c r="G2" t="str">
+        <v>startFrameIndex</v>
+      </c>
+      <c r="H2" t="str">
+        <v>endFrameIndex</v>
+      </c>
+      <c r="I2" t="str">
+        <v>startFrameDisplay</v>
+      </c>
+      <c r="J2" t="str">
+        <v>endFrameDisplay</v>
+      </c>
+      <c r="K2" t="str">
+        <v>startTimeSec</v>
+      </c>
+      <c r="L2" t="str">
+        <v>endTimeSec</v>
+      </c>
+      <c r="M2" t="str">
+        <v>entryOnsetTimeSec</v>
       </c>
       <c r="N2" t="str">
-        <v>auto</v>
+        <v>completionTimeSec</v>
       </c>
       <c r="O2" t="str">
-        <v>proposed</v>
+        <v>censorBoundaryTimeSec</v>
       </c>
       <c r="P2" t="str">
-        <v>medium</v>
-      </c>
-      <c r="Q2">
-        <v>1</v>
+        <v>origin</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>status</v>
       </c>
       <c r="R2" t="str">
-        <v>false</v>
+        <v>confidence</v>
+      </c>
+      <c r="S2" t="str">
+        <v>visitIndex</v>
+      </c>
+      <c r="T2" t="str">
+        <v>isRevisit</v>
+      </c>
+      <c r="U2" t="str">
+        <v>bodyEntryPath</v>
+      </c>
+      <c r="V2" t="str">
+        <v>bodyEntryVersion</v>
+      </c>
+      <c r="W2" t="str">
+        <v>pixelEvidenceComplete</v>
+      </c>
+      <c r="X2" t="str">
+        <v>notes</v>
       </c>
     </row>
     <row r="3">
@@ -1288,7 +1628,7 @@
         <v>8df6325a-52d4-482b-a20f-688ba96ae0f5</v>
       </c>
       <c r="B3" t="str">
-        <v>dd55033e-e80e-4725-aadc-df464b0a2d5c</v>
+        <v>b20de175-42d7-4c55-b8c8-32a957caf29c</v>
       </c>
       <c r="C3" t="str">
         <v>investigation</v>
@@ -1297,36 +1637,42 @@
         <v>investigation</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>150</v>
+      </c>
+      <c r="H3">
+        <v>265</v>
+      </c>
+      <c r="I3">
+        <v>151</v>
+      </c>
+      <c r="J3">
+        <v>266</v>
+      </c>
+      <c r="K3">
+        <v>5.066667</v>
+      </c>
+      <c r="L3">
+        <v>8.9</v>
+      </c>
+      <c r="P3" t="str">
+        <v>auto</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>proposed</v>
+      </c>
+      <c r="R3" t="str">
+        <v>medium</v>
+      </c>
+      <c r="S3">
         <v>1</v>
       </c>
-      <c r="G3">
-        <v>270</v>
-      </c>
-      <c r="H3">
-        <v>430</v>
-      </c>
-      <c r="I3">
-        <v>9.066667</v>
-      </c>
-      <c r="J3">
-        <v>14.433333</v>
-      </c>
-      <c r="N3" t="str">
-        <v>auto</v>
-      </c>
-      <c r="O3" t="str">
-        <v>proposed</v>
-      </c>
-      <c r="P3" t="str">
-        <v>medium</v>
-      </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
-      <c r="R3" t="str">
+      <c r="T3" t="str">
         <v>false</v>
       </c>
     </row>
@@ -1335,7 +1681,7 @@
         <v>8df6325a-52d4-482b-a20f-688ba96ae0f5</v>
       </c>
       <c r="B4" t="str">
-        <v>7521ef19-add7-4516-b3a1-8595d107dc4a</v>
+        <v>dd55033e-e80e-4725-aadc-df464b0a2d5c</v>
       </c>
       <c r="C4" t="str">
         <v>investigation</v>
@@ -1344,36 +1690,42 @@
         <v>investigation</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>536</v>
+        <v>270</v>
       </c>
       <c r="H4">
-        <v>647</v>
+        <v>430</v>
       </c>
       <c r="I4">
-        <v>17.966667</v>
+        <v>271</v>
       </c>
       <c r="J4">
-        <v>21.666667</v>
-      </c>
-      <c r="N4" t="str">
+        <v>431</v>
+      </c>
+      <c r="K4">
+        <v>9.066667</v>
+      </c>
+      <c r="L4">
+        <v>14.433333</v>
+      </c>
+      <c r="P4" t="str">
         <v>auto</v>
       </c>
-      <c r="O4" t="str">
+      <c r="Q4" t="str">
         <v>proposed</v>
       </c>
-      <c r="P4" t="str">
+      <c r="R4" t="str">
         <v>medium</v>
       </c>
-      <c r="Q4">
+      <c r="S4">
         <v>1</v>
       </c>
-      <c r="R4" t="str">
+      <c r="T4" t="str">
         <v>false</v>
       </c>
     </row>
@@ -1382,7 +1734,7 @@
         <v>8df6325a-52d4-482b-a20f-688ba96ae0f5</v>
       </c>
       <c r="B5" t="str">
-        <v>5b96f4a0-36a1-4d99-b81a-d1e97a9d4621</v>
+        <v>7521ef19-add7-4516-b3a1-8595d107dc4a</v>
       </c>
       <c r="C5" t="str">
         <v>investigation</v>
@@ -1391,37 +1743,43 @@
         <v>investigation</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>536</v>
+      </c>
+      <c r="H5">
+        <v>647</v>
+      </c>
+      <c r="I5">
+        <v>537</v>
+      </c>
+      <c r="J5">
+        <v>648</v>
+      </c>
+      <c r="K5">
+        <v>17.966667</v>
+      </c>
+      <c r="L5">
+        <v>21.666667</v>
+      </c>
+      <c r="P5" t="str">
+        <v>auto</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>proposed</v>
+      </c>
+      <c r="R5" t="str">
+        <v>medium</v>
+      </c>
+      <c r="S5">
         <v>1</v>
       </c>
-      <c r="G5">
-        <v>737</v>
-      </c>
-      <c r="H5">
-        <v>904</v>
-      </c>
-      <c r="I5">
-        <v>24.7</v>
-      </c>
-      <c r="J5">
-        <v>30.266667</v>
-      </c>
-      <c r="N5" t="str">
-        <v>auto</v>
-      </c>
-      <c r="O5" t="str">
-        <v>proposed</v>
-      </c>
-      <c r="P5" t="str">
-        <v>medium</v>
-      </c>
-      <c r="Q5">
-        <v>2</v>
-      </c>
-      <c r="R5" t="str">
-        <v>true</v>
+      <c r="T5" t="str">
+        <v>false</v>
       </c>
     </row>
     <row r="6">
@@ -1429,13 +1787,13 @@
         <v>8df6325a-52d4-482b-a20f-688ba96ae0f5</v>
       </c>
       <c r="B6" t="str">
-        <v>c417f59c-c9e9-49ff-ba29-d732c003160d</v>
+        <v>5b96f4a0-36a1-4d99-b81a-d1e97a9d4621</v>
       </c>
       <c r="C6" t="str">
-        <v>escape_completed</v>
+        <v>investigation</v>
       </c>
       <c r="D6" t="str">
-        <v>escape_completed_confirmed_candidate_hole</v>
+        <v>investigation</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -1444,49 +1802,115 @@
         <v>1</v>
       </c>
       <c r="G6">
+        <v>737</v>
+      </c>
+      <c r="H6">
+        <v>904</v>
+      </c>
+      <c r="I6">
+        <v>738</v>
+      </c>
+      <c r="J6">
+        <v>905</v>
+      </c>
+      <c r="K6">
+        <v>24.7</v>
+      </c>
+      <c r="L6">
+        <v>30.266667</v>
+      </c>
+      <c r="P6" t="str">
+        <v>auto</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>proposed</v>
+      </c>
+      <c r="R6" t="str">
+        <v>medium</v>
+      </c>
+      <c r="S6">
+        <v>2</v>
+      </c>
+      <c r="T6" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>8df6325a-52d4-482b-a20f-688ba96ae0f5</v>
+      </c>
+      <c r="B7" t="str">
+        <v>c417f59c-c9e9-49ff-ba29-d732c003160d</v>
+      </c>
+      <c r="C7" t="str">
+        <v>escape_completed</v>
+      </c>
+      <c r="D7" t="str">
+        <v>escape_completed_confirmed_candidate_hole</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
         <v>785</v>
       </c>
-      <c r="H6">
+      <c r="H7">
         <v>880</v>
       </c>
-      <c r="I6">
+      <c r="I7">
+        <v>786</v>
+      </c>
+      <c r="J7">
+        <v>881</v>
+      </c>
+      <c r="K7">
         <v>26.3</v>
       </c>
-      <c r="J6">
+      <c r="L7">
         <v>29.466667</v>
       </c>
-      <c r="K6">
+      <c r="M7">
         <v>26.3</v>
       </c>
-      <c r="L6">
+      <c r="N7">
         <v>29.466667</v>
       </c>
-      <c r="M6">
+      <c r="O7">
         <v>30.266667</v>
       </c>
-      <c r="N6" t="str">
+      <c r="P7" t="str">
         <v>auto</v>
       </c>
-      <c r="O6" t="str">
+      <c r="Q7" t="str">
         <v>confirmed</v>
       </c>
-      <c r="P6" t="str">
+      <c r="R7" t="str">
         <v>high</v>
       </c>
-      <c r="T6">
+      <c r="V7">
         <v>3</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:X7"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:X7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C42"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="36.83203125" customWidth="1"/>
+    <col min="3" max="3" width="48.83203125" customWidth="1"/>
+    <col min="4" max="4" width="48.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1507,7 +1931,7 @@
         <v>exportedAt</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-09-07T19:54:09.007Z</v>
+        <v>2026-09-07T20:08:18.622Z</v>
       </c>
     </row>
     <row r="3">
@@ -1948,15 +2372,22 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C42"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C42"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F17"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="36.83203125" customWidth="1"/>
+    <col min="3" max="3" width="48.83203125" customWidth="1"/>
+    <col min="4" max="4" width="48.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2284,15 +2715,22 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F17"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:F17"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:U2"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="36.83203125" customWidth="1"/>
+    <col min="3" max="3" width="48.83203125" customWidth="1"/>
+    <col min="4" max="4" width="48.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2413,6 +2851,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:U2"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:U2"/>
   </ignoredErrors>
